--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
+        <v>500</v>
+      </c>
+      <c r="L15" s="15">
         <v>200</v>
       </c>
-      <c r="L15" s="15">
-        <v>50</v>
-      </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
         <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J16" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.842105263157</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.666666666666</v>
+        <v>-91.764705882352</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
-      </c>
-      <c r="D17" s="14">
-        <v>7</v>
-      </c>
-      <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>-17.857142857142</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J17" s="14">
         <v>35</v>
       </c>
       <c r="K17" s="15">
-        <v>-17.142857142857</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-25.641025641025</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="M17" s="15">
-        <v>26.086956521739</v>
+        <v>40</v>
       </c>
       <c r="N17" s="15">
-        <v>-3.333333333333</v>
+        <v>-5.405405405405</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
         <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.111111111111</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.636363636363</v>
+        <v>-67.857142857142</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.266272189349</v>
+        <v>-95.431472081218</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>3</v>
+      </c>
+      <c r="D19" s="14">
         <v>6</v>
       </c>
-      <c r="D19" s="14">
-        <v>9</v>
-      </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
         <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>-32.142857142857</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="I19" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J19" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K19" s="15">
-        <v>-39.473684210526</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L19" s="15">
         <v>-50</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.333333333333</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N19" s="15">
-        <v>-66.176470588235</v>
+        <v>-65.333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>300</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>20</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I20" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J20" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K20" s="15">
-        <v>28.571428571428</v>
+        <v>16</v>
       </c>
       <c r="L20" s="15">
-        <v>58.823529411764</v>
+        <v>26.086956521739</v>
       </c>
       <c r="M20" s="15">
-        <v>-12.903225806451</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.398340248962</v>
+        <v>-94.659300184162</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.606741573033</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="I21" s="17">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="J21" s="17">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.445378151260</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.969696969697</v>
+        <v>-20</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.872483221476</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="N21" s="18">
-        <v>-88.504464285714</v>
+        <v>-88.292682926829</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-53.846153846153</v>
+        <v>13.043478260869</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H24" s="15">
-        <v>-30.303030303030</v>
+        <v>-23.711340206185</v>
       </c>
       <c r="I24" s="14">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="J24" s="14">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="K24" s="15">
-        <v>-32.592592592592</v>
+        <v>-25.316455696202</v>
       </c>
       <c r="L24" s="15">
-        <v>-37.241379310344</v>
+        <v>-30.177514792899</v>
       </c>
       <c r="M24" s="15">
-        <v>-6.185567010309</v>
+        <v>7.272727272727</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-37.5</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F25" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G25" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.684210526315</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I25" s="14">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J25" s="14">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="K25" s="15">
-        <v>-23.404255319148</v>
+        <v>-14.754098360655</v>
       </c>
       <c r="L25" s="15">
-        <v>-49.295774647887</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-36.363636363636</v>
+        <v>140</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.5</v>
+        <v>19.230769230769</v>
       </c>
       <c r="I26" s="14">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J26" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K26" s="15">
-        <v>-15.909090909090</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="L26" s="15">
-        <v>-42.1875</v>
+        <v>-32.394366197183</v>
       </c>
       <c r="M26" s="15">
-        <v>-45.588235294117</v>
+        <v>-36</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>33.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L28" s="15">
-        <v>14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
@@ -920,7 +920,7 @@
         <v>500</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="E16" s="15">
-        <v>-50</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-38.461538461538</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
         <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-28</v>
       </c>
       <c r="M16" s="15">
-        <v>-66.666666666666</v>
+        <v>-61.702127659574</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.764705882352</v>
+        <v>-90.575916230366</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="D17" s="14">
+        <v>2</v>
+      </c>
+      <c r="E17" s="15">
+        <v>400</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>14.285714285714</v>
+        <v>106.666666666667</v>
       </c>
       <c r="I17" s="14">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="J17" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>27.027027027027</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.634146341463</v>
+        <v>-6</v>
       </c>
       <c r="M17" s="15">
-        <v>40</v>
+        <v>38.235294117647</v>
       </c>
       <c r="N17" s="15">
-        <v>-5.405405405405</v>
+        <v>14.634146341463</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14">
+        <v>11</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-54.545454545454</v>
+      </c>
+      <c r="I18" s="14">
         <v>10</v>
       </c>
-      <c r="H18" s="15">
-        <v>-50</v>
-      </c>
-      <c r="I18" s="14">
-        <v>9</v>
-      </c>
       <c r="J18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.714285714285</v>
+        <v>-37.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.181818181818</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.857142857142</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.431472081218</v>
+        <v>-95.348837209302</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>60</v>
       </c>
       <c r="F19" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-34.482758620689</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J19" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K19" s="15">
-        <v>-40.909090909090</v>
+        <v>-30.612244897959</v>
       </c>
       <c r="L19" s="15">
-        <v>-50</v>
+        <v>-45.161290322580</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.529411764705</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="N19" s="15">
-        <v>-65.333333333333</v>
+        <v>-60.919540229885</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>7</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>4</v>
-      </c>
       <c r="E20" s="15">
-        <v>-25</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>15.384615384615</v>
+        <v>90</v>
       </c>
       <c r="I20" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J20" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>16</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L20" s="15">
-        <v>26.086956521739</v>
+        <v>24.137931034482</v>
       </c>
       <c r="M20" s="15">
-        <v>-14.705882352941</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.659300184162</v>
+        <v>-94.019933554817</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.909090909090</v>
+        <v>15.789473684210</v>
       </c>
       <c r="I21" s="17">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="J21" s="17">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-20</v>
+        <v>-16.483516483516</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.829268292682</v>
+        <v>-21.649484536082</v>
       </c>
       <c r="N21" s="18">
-        <v>-88.292682926829</v>
+        <v>-86.654960491659</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>13.043478260869</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.711340206185</v>
+        <v>-21.782178217821</v>
       </c>
       <c r="I24" s="14">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="J24" s="14">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.316455696202</v>
+        <v>-23.783783783783</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.177514792899</v>
+        <v>-30.198019801980</v>
       </c>
       <c r="M24" s="15">
-        <v>7.272727272727</v>
+        <v>10.15625</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E25" s="15">
-        <v>14.285714285714</v>
+        <v>-55</v>
       </c>
       <c r="F25" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G25" s="14">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H25" s="15">
-        <v>-22.727272727272</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="I25" s="14">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J25" s="14">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="K25" s="15">
-        <v>-14.754098360655</v>
+        <v>-24.691358024691</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.095238095238</v>
+        <v>-39</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>140</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>19.230769230769</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I26" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J26" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.040816326530</v>
+        <v>1.818181818181</v>
       </c>
       <c r="L26" s="15">
-        <v>-32.394366197183</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M26" s="15">
-        <v>-36</v>
+        <v>-30</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>4</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1412,7 +1412,7 @@
         <v>40</v>
       </c>
       <c r="L27" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>200</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>10</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="15">
         <v>-100</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>-100</v>
       </c>
       <c r="M29" s="15">
         <v>-100</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="15">
         <v>-100</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>-100</v>
       </c>
       <c r="M30" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-20</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-10</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L16" s="15">
-        <v>-28</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-61.702127659574</v>
+        <v>-59.183673469387</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.575916230366</v>
+        <v>-90.783410138248</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>400</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>106.666666666667</v>
+        <v>56.25</v>
       </c>
       <c r="I17" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J17" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K17" s="15">
-        <v>27.027027027027</v>
+        <v>15.909090909090</v>
       </c>
       <c r="L17" s="15">
-        <v>-6</v>
+        <v>-8.928571428571</v>
       </c>
       <c r="M17" s="15">
-        <v>38.235294117647</v>
+        <v>41.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>14.634146341463</v>
+        <v>10.869565217391</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F18" s="14">
         <v>2</v>
       </c>
-      <c r="E18" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F18" s="14">
-        <v>5</v>
-      </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-54.545454545454</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="I18" s="14">
         <v>10</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.5</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.076923076923</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.666666666666</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.348837209302</v>
+        <v>-95.780590717299</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>-17.857142857142</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J19" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K19" s="15">
-        <v>-30.612244897959</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="L19" s="15">
-        <v>-45.161290322580</v>
+        <v>-42.253521126760</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.444444444444</v>
+        <v>-18</v>
       </c>
       <c r="N19" s="15">
-        <v>-60.919540229885</v>
+        <v>-58.585858585858</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>133.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>90</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K20" s="15">
-        <v>28.571428571428</v>
+        <v>21.875</v>
       </c>
       <c r="L20" s="15">
-        <v>24.137931034482</v>
+        <v>11.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>-2.702702702702</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.019933554817</v>
+        <v>-94.009216589861</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>150</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>15.789473684210</v>
+        <v>4.054054054054</v>
       </c>
       <c r="I21" s="17">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J21" s="17">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>-2.339181286549</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.483516483516</v>
+        <v>-21.962616822429</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.649484536082</v>
+        <v>-22.325581395348</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.654960491659</v>
+        <v>-86.671987230646</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.518518518518</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15">
-        <v>-21.782178217821</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I24" s="14">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J24" s="14">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.783783783783</v>
+        <v>-25.118483412322</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.198019801980</v>
+        <v>-31.896551724137</v>
       </c>
       <c r="M24" s="15">
-        <v>10.15625</v>
+        <v>11.267605633802</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-55</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F25" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G25" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H25" s="15">
-        <v>-26.923076923076</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I25" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="J25" s="14">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.691358024691</v>
+        <v>-24.468085106383</v>
       </c>
       <c r="L25" s="15">
-        <v>-39</v>
+        <v>-36.036036036036</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>3.448275862068</v>
+        <v>19.354838709677</v>
       </c>
       <c r="I26" s="14">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J26" s="14">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="K26" s="15">
-        <v>1.818181818181</v>
+        <v>3.125</v>
       </c>
       <c r="L26" s="15">
-        <v>-26.315789473684</v>
+        <v>-22.352941176470</v>
       </c>
       <c r="M26" s="15">
-        <v>-30</v>
+        <v>-27.472527472527</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>40</v>
       </c>
       <c r="L27" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>42.857142857142</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>62.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -885,15 +885,15 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>28.571428571428</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
         <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.761904761904</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="M16" s="15">
-        <v>-59.183673469387</v>
+        <v>-56</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.783410138248</v>
+        <v>-90.756302521008</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,31 +984,31 @@
         <v>-57.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
         <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>56.25</v>
+        <v>37.5</v>
       </c>
       <c r="I17" s="14">
+        <v>54</v>
+      </c>
+      <c r="J17" s="14">
         <v>51</v>
       </c>
-      <c r="J17" s="14">
-        <v>44</v>
-      </c>
       <c r="K17" s="15">
-        <v>15.909090909090</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.928571428571</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="M17" s="15">
-        <v>41.666666666666</v>
+        <v>38.461538461538</v>
       </c>
       <c r="N17" s="15">
-        <v>10.869565217391</v>
+        <v>3.846153846153</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,81 +1016,81 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-84.615384615384</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J18" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="15">
-        <v>-47.368421052631</v>
+        <v>-30</v>
       </c>
       <c r="L18" s="15">
-        <v>-44.444444444444</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M18" s="15">
-        <v>-72.222222222222</v>
+        <v>-65.853658536585</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.780590717299</v>
+        <v>-94.636015325670</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14">
-        <v>6</v>
+      <c r="C19" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D19" s="14">
         <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I19" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J19" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.641509433962</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L19" s="15">
-        <v>-42.253521126760</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M19" s="15">
-        <v>-18</v>
+        <v>-23.636363636363</v>
       </c>
       <c r="N19" s="15">
-        <v>-58.585858585858</v>
+        <v>-61.111111111111</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I20" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J20" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K20" s="15">
-        <v>21.875</v>
+        <v>18.421052631578</v>
       </c>
       <c r="L20" s="15">
-        <v>11.428571428571</v>
+        <v>21.621621621621</v>
       </c>
       <c r="M20" s="15">
-        <v>-9.302325581395</v>
+        <v>2.272727272727</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.009216589861</v>
+        <v>-93.607954545454</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.315789473684</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
-        <v>4.054054054054</v>
+        <v>8.571428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J21" s="17">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.339181286549</v>
+        <v>-2.645502645502</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.962616822429</v>
+        <v>-21.030042918454</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.325581395348</v>
+        <v>-20</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.671987230646</v>
+        <v>-86.539868324798</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
         <v>50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-34.615384615384</v>
+        <v>31.578947368421</v>
       </c>
       <c r="F24" s="14">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.529411764705</v>
+        <v>-7.368421052631</v>
       </c>
       <c r="I24" s="14">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="J24" s="14">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.118483412322</v>
+        <v>-21.304347826087</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.896551724137</v>
+        <v>-27.888446215139</v>
       </c>
       <c r="M24" s="15">
-        <v>11.267605633802</v>
+        <v>19.078947368421</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.076923076923</v>
+        <v>200</v>
       </c>
       <c r="F25" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G25" s="14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.272727272727</v>
+        <v>-12</v>
       </c>
       <c r="I25" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="J25" s="14">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.468085106383</v>
+        <v>-17.525773195876</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.036036036036</v>
+        <v>-33.884297520661</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="F26" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>19.354838709677</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I26" s="14">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="J26" s="14">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="K26" s="15">
-        <v>3.125</v>
+        <v>-1.25</v>
       </c>
       <c r="L26" s="15">
-        <v>-22.352941176470</v>
+        <v>-19.387755102040</v>
       </c>
       <c r="M26" s="15">
-        <v>-27.472527472527</v>
+        <v>-26.168224299065</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,22 +1397,22 @@
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>44.444444444444</v>
+        <v>54.545454545454</v>
       </c>
       <c r="L28" s="15">
-        <v>62.5</v>
+        <v>88.888888888888</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="15">
         <v>-100</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -885,24 +885,24 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -920,54 +920,54 @@
         <v>500</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I16" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>4.761904761904</v>
+        <v>-12.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.142857142857</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="M16" s="15">
-        <v>-56</v>
+        <v>-60.377358490566</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.756302521008</v>
+        <v>-91.796875</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,122 +975,122 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>37.5</v>
+        <v>4</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J17" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K17" s="15">
-        <v>5.882352941176</v>
+        <v>5</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.475409836065</v>
+        <v>-11.267605633802</v>
       </c>
       <c r="M17" s="15">
-        <v>38.461538461538</v>
+        <v>46.511627906976</v>
       </c>
       <c r="N17" s="15">
-        <v>3.846153846153</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>4</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-58.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>-30</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L18" s="15">
-        <v>-26.315789473684</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.853658536585</v>
+        <v>-64</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.636015325670</v>
+        <v>-93.639575971731</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>20</v>
+      <c r="C19" s="14">
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-100</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.263157894736</v>
+        <v>5</v>
       </c>
       <c r="I19" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J19" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K19" s="15">
-        <v>-26.315789473684</v>
+        <v>-25</v>
       </c>
       <c r="L19" s="15">
-        <v>-45.454545454545</v>
+        <v>-44.186046511627</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.636363636363</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="N19" s="15">
-        <v>-61.111111111111</v>
+        <v>-57.894736842105</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>8</v>
+      </c>
+      <c r="D20" s="14">
+        <v>7</v>
+      </c>
+      <c r="E20" s="15">
+        <v>14.285714285714</v>
+      </c>
+      <c r="F20" s="14">
+        <v>24</v>
+      </c>
+      <c r="G20" s="14">
+        <v>20</v>
+      </c>
+      <c r="H20" s="15">
+        <v>20</v>
+      </c>
+      <c r="I20" s="14">
+        <v>53</v>
+      </c>
+      <c r="J20" s="14">
+        <v>45</v>
+      </c>
+      <c r="K20" s="15">
+        <v>17.777777777777</v>
+      </c>
+      <c r="L20" s="15">
+        <v>17.777777777777</v>
+      </c>
+      <c r="M20" s="15">
         <v>6</v>
       </c>
-      <c r="D20" s="14">
-        <v>6</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>19</v>
-      </c>
-      <c r="G20" s="14">
-        <v>17</v>
-      </c>
-      <c r="H20" s="15">
-        <v>11.764705882352</v>
-      </c>
-      <c r="I20" s="14">
-        <v>45</v>
-      </c>
-      <c r="J20" s="14">
-        <v>38</v>
-      </c>
-      <c r="K20" s="15">
-        <v>18.421052631578</v>
-      </c>
-      <c r="L20" s="15">
-        <v>21.621621621621</v>
-      </c>
-      <c r="M20" s="15">
-        <v>2.272727272727</v>
-      </c>
       <c r="N20" s="15">
-        <v>-93.607954545454</v>
+        <v>-93.071895424836</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.111111111111</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="F21" s="17">
+        <v>88</v>
+      </c>
+      <c r="G21" s="17">
         <v>76</v>
       </c>
-      <c r="G21" s="17">
-        <v>70</v>
-      </c>
       <c r="H21" s="18">
-        <v>8.571428571428</v>
+        <v>15.789473684210</v>
       </c>
       <c r="I21" s="17">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="J21" s="17">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.645502645502</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.030042918454</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="M21" s="18">
-        <v>-20</v>
+        <v>-17.96875</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.539868324798</v>
+        <v>-85.877605917955</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>31.578947368421</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F24" s="14">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.368421052631</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J24" s="14">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.304347826087</v>
+        <v>-23.387096774193</v>
       </c>
       <c r="L24" s="15">
-        <v>-27.888446215139</v>
+        <v>-31.407942238267</v>
       </c>
       <c r="M24" s="15">
-        <v>19.078947368421</v>
+        <v>15.853658536585</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>200</v>
+        <v>-62.5</v>
       </c>
       <c r="F25" s="14">
+        <v>27</v>
+      </c>
+      <c r="G25" s="14">
         <v>44</v>
       </c>
-      <c r="G25" s="14">
-        <v>50</v>
-      </c>
       <c r="H25" s="15">
-        <v>-12</v>
+        <v>-38.636363636363</v>
       </c>
       <c r="I25" s="14">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J25" s="14">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.525773195876</v>
+        <v>-24.761904761904</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.884297520661</v>
+        <v>-41.044776119403</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-18.75</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F26" s="14">
         <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="I26" s="14">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J26" s="14">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.387755102040</v>
+        <v>-19.090909090909</v>
       </c>
       <c r="M26" s="15">
-        <v>-26.168224299065</v>
+        <v>-27.049180327868</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>200</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>8</v>
@@ -1412,7 +1412,7 @@
         <v>60</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>10</v>
-      </c>
-      <c r="G28" s="14">
-        <v>5</v>
       </c>
       <c r="H28" s="15">
         <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>54.545454545454</v>
+        <v>63.636363636363</v>
       </c>
       <c r="L28" s="15">
-        <v>88.888888888888</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,79 +895,79 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>500</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>75</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.5</v>
+        <v>-21.875</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.736842105263</v>
+        <v>-41.860465116279</v>
       </c>
       <c r="M16" s="15">
-        <v>-60.377358490566</v>
+        <v>-57.627118644067</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.796875</v>
+        <v>-91.039426523297</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>4</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="I17" s="14">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J17" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K17" s="15">
-        <v>5</v>
+        <v>6.060606060606</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.267605633802</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>46.511627906976</v>
+        <v>52.173913043478</v>
       </c>
       <c r="N17" s="15">
-        <v>5</v>
+        <v>11.111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
+        <v>8</v>
+      </c>
+      <c r="G18" s="14">
         <v>9</v>
       </c>
-      <c r="G18" s="14">
-        <v>7</v>
-      </c>
       <c r="H18" s="15">
-        <v>28.571428571428</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.285714285714</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="15">
-        <v>-5.263157894736</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M18" s="15">
-        <v>-64</v>
+        <v>-67.741935483871</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.639575971731</v>
+        <v>-93.377483443708</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>75</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H19" s="15">
-        <v>5</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I19" s="14">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J19" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K19" s="15">
-        <v>-25</v>
+        <v>-19.117647058823</v>
       </c>
       <c r="L19" s="15">
-        <v>-44.186046511627</v>
+        <v>-40.860215053763</v>
       </c>
       <c r="M19" s="15">
-        <v>-18.644067796610</v>
+        <v>-14.0625</v>
       </c>
       <c r="N19" s="15">
-        <v>-57.894736842105</v>
+        <v>-53.781512605042</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
         <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J20" s="14">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K20" s="15">
-        <v>17.777777777777</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L20" s="15">
-        <v>17.777777777777</v>
+        <v>22.448979591836</v>
       </c>
       <c r="M20" s="15">
-        <v>6</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.071895424836</v>
+        <v>-92.744860943168</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.814814814814</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H21" s="18">
-        <v>15.789473684210</v>
+        <v>-13.684210526315</v>
       </c>
       <c r="I21" s="17">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="J21" s="17">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.777777777777</v>
+        <v>-3.643724696356</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.454545454545</v>
+        <v>-16.783216783216</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.96875</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.877605917955</v>
+        <v>-85.115697310819</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E24" s="15">
-        <v>-27.777777777777</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H24" s="15">
-        <v>-21.111111111111</v>
+        <v>-25.252525252525</v>
       </c>
       <c r="I24" s="14">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="J24" s="14">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.387096774193</v>
+        <v>-25.352112676056</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.407942238267</v>
+        <v>-32.698412698412</v>
       </c>
       <c r="M24" s="15">
-        <v>15.853658536585</v>
+        <v>19.101123595505</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-62.5</v>
+        <v>-68.181818181818</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G25" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.636363636363</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="I25" s="14">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J25" s="14">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.761904761904</v>
+        <v>-32.283464566929</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.044776119403</v>
+        <v>-44.516129032258</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>11.111111111111</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G26" s="14">
         <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>10</v>
+        <v>27.5</v>
       </c>
       <c r="I26" s="14">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="J26" s="14">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.090909090909</v>
+        <v>-17.322834645669</v>
       </c>
       <c r="M26" s="15">
-        <v>-27.049180327868</v>
+        <v>-17.96875</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>60</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L27" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>7</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-71.428571428571</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I28" s="14">
+        <v>20</v>
+      </c>
+      <c r="J28" s="14">
         <v>18</v>
       </c>
-      <c r="J28" s="14">
-        <v>11</v>
-      </c>
       <c r="K28" s="15">
-        <v>63.636363636363</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>122.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,31 +1484,31 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,23 +1525,23 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,36 +870,36 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -911,22 +911,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L15" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
         <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K16" s="15">
-        <v>-21.875</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.860465116279</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.627118644067</v>
+        <v>-58.208955223880</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.039426523297</v>
+        <v>-90.604026845637</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>16.666666666666</v>
+        <v>80</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-24.137931034482</v>
+        <v>3.703703703703</v>
       </c>
       <c r="I17" s="14">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K17" s="15">
-        <v>6.060606060606</v>
+        <v>11.267605633802</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.666666666666</v>
+        <v>2.597402597402</v>
       </c>
       <c r="M17" s="15">
-        <v>52.173913043478</v>
+        <v>54.901960784313</v>
       </c>
       <c r="N17" s="15">
-        <v>11.111111111111</v>
+        <v>8.219178082191</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
         <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-11.111111111111</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I18" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-20</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L18" s="15">
-        <v>-4.761904761904</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.741935483871</v>
+        <v>-62.686567164179</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.377483443708</v>
+        <v>-92.283950617283</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>75</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>5.263157894736</v>
+        <v>4.166666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="J19" s="14">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.117647058823</v>
+        <v>-11.688311688311</v>
       </c>
       <c r="L19" s="15">
-        <v>-40.860215053763</v>
+        <v>-28.421052631578</v>
       </c>
       <c r="M19" s="15">
-        <v>-14.0625</v>
+        <v>-6.849315068493</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.781512605042</v>
+        <v>-45.6</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I20" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J20" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K20" s="15">
-        <v>15.384615384615</v>
+        <v>17.543859649122</v>
       </c>
       <c r="L20" s="15">
-        <v>22.448979591836</v>
+        <v>28.846153846153</v>
       </c>
       <c r="M20" s="15">
-        <v>9.090909090909</v>
+        <v>11.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.744860943168</v>
+        <v>-92.505592841163</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.903225806451</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="G21" s="17">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.684210526315</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="J21" s="17">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.643724696356</v>
+        <v>0.727272727272</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.783216783216</v>
+        <v>-6.418918918918</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.073170731707</v>
+        <v>-13.166144200627</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.115697310819</v>
+        <v>-83.932714617169</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,10 +1207,10 @@
         <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.666666666666</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="F24" s="14">
         <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.252525252525</v>
+        <v>-22.105263157894</v>
       </c>
       <c r="I24" s="14">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="J24" s="14">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.352112676056</v>
+        <v>-25.163398692810</v>
       </c>
       <c r="L24" s="15">
-        <v>-32.698412698412</v>
+        <v>-32.047477744807</v>
       </c>
       <c r="M24" s="15">
-        <v>19.101123595505</v>
+        <v>18.652849740932</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-68.181818181818</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F25" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
         <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>-39.130434782608</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="I25" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J25" s="14">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.283464566929</v>
+        <v>-32.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>-44.516129032258</v>
+        <v>-44.047619047619</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>166.666666666667</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H26" s="15">
-        <v>27.5</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="I26" s="14">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="J26" s="14">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="K26" s="15">
-        <v>10.526315789473</v>
+        <v>-0.854700854700</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.322834645669</v>
+        <v>-16.546762589928</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.96875</v>
+        <v>-16.546762589928</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
@@ -1403,16 +1403,16 @@
         <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L27" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-71.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>11.111111111111</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L28" s="15">
-        <v>122.222222222222</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>2</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>2</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-50</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>2</v>
+      </c>
+      <c r="K33" s="15">
+        <v>-50</v>
       </c>
       <c r="L33" s="15">
         <v>-66.666666666666</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>166.666666666667</v>
+        <v>233.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>14.285714285714</v>
+        <v>11.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="E16" s="15">
-        <v>200</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
         <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J16" s="14">
         <v>33</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.151515151515</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="L16" s="15">
-        <v>-34.883720930232</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.208955223880</v>
+        <v>-59.722222222222</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.604026845637</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
         <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>3.703703703703</v>
+        <v>48</v>
       </c>
       <c r="I17" s="14">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K17" s="15">
-        <v>11.267605633802</v>
+        <v>19.736842105263</v>
       </c>
       <c r="L17" s="15">
-        <v>2.597402597402</v>
+        <v>10.975609756097</v>
       </c>
       <c r="M17" s="15">
-        <v>54.901960784313</v>
+        <v>65.454545454545</v>
       </c>
       <c r="N17" s="15">
-        <v>8.219178082191</v>
+        <v>12.345679012345</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
         <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.428571428571</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-24.242424242424</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.686567164179</v>
+        <v>-63.380281690140</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.283950617283</v>
+        <v>-92.463768115942</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>44.444444444444</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
+        <v>29</v>
+      </c>
+      <c r="G19" s="14">
         <v>25</v>
       </c>
-      <c r="G19" s="14">
-        <v>24</v>
-      </c>
       <c r="H19" s="15">
-        <v>4.166666666666</v>
+        <v>16</v>
       </c>
       <c r="I19" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J19" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.688311688311</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.421052631578</v>
+        <v>-28</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.849315068493</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.6</v>
+        <v>-45.864661654135</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>6</v>
+      </c>
+      <c r="D20" s="14">
         <v>7</v>
       </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
       <c r="E20" s="15">
-        <v>40</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F20" s="14">
         <v>28</v>
       </c>
       <c r="G20" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>12</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I20" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J20" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K20" s="15">
-        <v>17.543859649122</v>
+        <v>14.0625</v>
       </c>
       <c r="L20" s="15">
-        <v>28.846153846153</v>
+        <v>21.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>11.666666666666</v>
+        <v>12.307692307692</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.505592841163</v>
+        <v>-92.323869610935</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>35.714285714285</v>
+        <v>36.842105263157</v>
       </c>
       <c r="F21" s="17">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="G21" s="17">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>7.619047619047</v>
       </c>
       <c r="I21" s="17">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="J21" s="17">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="K21" s="18">
-        <v>0.727272727272</v>
+        <v>3.061224489795</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.418918918918</v>
+        <v>-4.716981132075</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.166144200627</v>
+        <v>-11.403508771929</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.932714617169</v>
+        <v>-83.541553503530</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-22.727272727272</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>-22.105263157894</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="I24" s="14">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="J24" s="14">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.163398692810</v>
+        <v>-23.952095808383</v>
       </c>
       <c r="L24" s="15">
-        <v>-32.047477744807</v>
+        <v>-30.601092896174</v>
       </c>
       <c r="M24" s="15">
-        <v>18.652849740932</v>
+        <v>23.902439024390</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-38.461538461538</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G25" s="14">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="H25" s="15">
-        <v>-43.478260869565</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="I25" s="14">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="J25" s="14">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.857142857142</v>
+        <v>-30.322580645161</v>
       </c>
       <c r="L25" s="15">
-        <v>-44.047619047619</v>
+        <v>-38.983050847457</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>122.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G26" s="14">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.660377358490</v>
+        <v>23.913043478260</v>
       </c>
       <c r="I26" s="14">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="J26" s="14">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.854700854700</v>
+        <v>7.936507936507</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.546762589928</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.546762589928</v>
+        <v>-7.482993197278</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>57.142857142857</v>
+        <v>62.5</v>
       </c>
       <c r="L27" s="15">
-        <v>57.142857142857</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>10.526315789473</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L28" s="15">
-        <v>133.333333333333</v>
+        <v>144.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>2</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,30 +870,30 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N14" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>233.333333333333</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+        <v>80</v>
+      </c>
+      <c r="M15" s="15">
+        <v>800</v>
       </c>
       <c r="N15" s="15">
-        <v>11.111111111111</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.121212121212</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.555555555555</v>
+        <v>-37.254901960784</v>
       </c>
       <c r="M16" s="15">
-        <v>-59.722222222222</v>
+        <v>-56.756756756756</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.909090909090</v>
+        <v>-90.560471976401</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>140</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>48</v>
+        <v>39.130434782608</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J17" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K17" s="15">
-        <v>19.736842105263</v>
+        <v>15.662650602409</v>
       </c>
       <c r="L17" s="15">
-        <v>10.975609756097</v>
+        <v>7.865168539325</v>
       </c>
       <c r="M17" s="15">
-        <v>65.454545454545</v>
+        <v>62.711864406779</v>
       </c>
       <c r="N17" s="15">
-        <v>12.345679012345</v>
+        <v>10.344827586206</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>400</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
         <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-53.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-25.714285714285</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>6.896551724137</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.380281690140</v>
+        <v>-60.256410256410</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.463768115942</v>
+        <v>-91.621621621621</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
         <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>16</v>
+        <v>38.095238095238</v>
       </c>
       <c r="I19" s="14">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J19" s="14">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.195121951219</v>
+        <v>-9.411764705882</v>
       </c>
       <c r="L19" s="15">
-        <v>-28</v>
+        <v>-24.509803921568</v>
       </c>
       <c r="M19" s="15">
-        <v>-7.692307692307</v>
+        <v>-10.465116279069</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.864661654135</v>
+        <v>-45.774647887323</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
         <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F20" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G20" s="14">
         <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>7.692307692307</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I20" s="14">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J20" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K20" s="15">
-        <v>14.0625</v>
+        <v>16.901408450704</v>
       </c>
       <c r="L20" s="15">
-        <v>21.666666666666</v>
+        <v>23.880597014925</v>
       </c>
       <c r="M20" s="15">
-        <v>12.307692307692</v>
+        <v>22.058823529411</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.323869610935</v>
+        <v>-91.822660098522</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>36.842105263157</v>
+        <v>45</v>
       </c>
       <c r="F21" s="17">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G21" s="17">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H21" s="18">
-        <v>7.619047619047</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="J21" s="17">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="K21" s="18">
-        <v>3.061224489795</v>
+        <v>5.414012738853</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.716981132075</v>
+        <v>-3.498542274052</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.403508771929</v>
+        <v>-9.809264305177</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.541553503530</v>
+        <v>-83.172343670564</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.714285714285</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G24" s="14">
         <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.923076923076</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="14">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="J24" s="14">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.952095808383</v>
+        <v>-23.579545454545</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.601092896174</v>
+        <v>-32.581453634085</v>
       </c>
       <c r="M24" s="15">
-        <v>23.902439024390</v>
+        <v>24.537037037037</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-13.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>-44.827586206896</v>
+        <v>-48.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J25" s="14">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="K25" s="15">
-        <v>-30.322580645161</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.983050847457</v>
+        <v>-43.005181347150</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>122.222222222222</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F26" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G26" s="14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>23.913043478260</v>
+        <v>34.090909090909</v>
       </c>
       <c r="I26" s="14">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="J26" s="14">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K26" s="15">
-        <v>7.936507936507</v>
+        <v>11.278195488721</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.526315789473</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.482993197278</v>
+        <v>-5.732484076433</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
@@ -1403,16 +1403,16 @@
         <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>85.714285714285</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I28" s="14">
+        <v>26</v>
+      </c>
+      <c r="J28" s="14">
         <v>22</v>
       </c>
-      <c r="J28" s="14">
-        <v>21</v>
-      </c>
       <c r="K28" s="15">
-        <v>4.761904761904</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L28" s="15">
-        <v>144.444444444444</v>
+        <v>160</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1616,14 +1616,14 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
       </c>
       <c r="H33" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>50</v>
+        <v>4</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>80</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N15" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -943,31 +943,31 @@
         <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
+        <v>160</v>
+      </c>
+      <c r="I16" s="14">
+        <v>37</v>
+      </c>
+      <c r="J16" s="14">
+        <v>37</v>
+      </c>
+      <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="I16" s="14">
-        <v>32</v>
-      </c>
-      <c r="J16" s="14">
-        <v>35</v>
-      </c>
-      <c r="K16" s="15">
-        <v>-8.571428571428</v>
-      </c>
       <c r="L16" s="15">
-        <v>-37.254901960784</v>
+        <v>-28.846153846153</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.756756756756</v>
+        <v>-50.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.560471976401</v>
+        <v>-89.664804469273</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>5</v>
+      </c>
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="14">
-        <v>7</v>
-      </c>
       <c r="E17" s="15">
-        <v>-57.142857142857</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>39.130434782608</v>
+        <v>45</v>
       </c>
       <c r="I17" s="14">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J17" s="14">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K17" s="15">
-        <v>15.662650602409</v>
+        <v>17.441860465116</v>
       </c>
       <c r="L17" s="15">
-        <v>7.865168539325</v>
+        <v>6.315789473684</v>
       </c>
       <c r="M17" s="15">
-        <v>62.711864406779</v>
+        <v>57.8125</v>
       </c>
       <c r="N17" s="15">
-        <v>10.344827586206</v>
+        <v>9.782608695652</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>400</v>
+        <v>2</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I18" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
         <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-13.888888888888</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>6.896551724137</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>-60.256410256410</v>
+        <v>-58.75</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.621621621621</v>
+        <v>-91.624365482233</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-30</v>
       </c>
       <c r="F19" s="14">
         <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>38.095238095238</v>
+        <v>7.407407407407</v>
       </c>
       <c r="I19" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J19" s="14">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.411764705882</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.509803921568</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M19" s="15">
-        <v>-10.465116279069</v>
+        <v>-6.593406593406</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.774647887323</v>
+        <v>-44.078947368421</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,13 +1098,13 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
         <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>30</v>
@@ -1116,22 +1116,22 @@
         <v>15.384615384615</v>
       </c>
       <c r="I20" s="14">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J20" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K20" s="15">
-        <v>16.901408450704</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L20" s="15">
-        <v>23.880597014925</v>
+        <v>26.760563380281</v>
       </c>
       <c r="M20" s="15">
-        <v>22.058823529411</v>
+        <v>21.621621621621</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.822660098522</v>
+        <v>-91.682070240295</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>45</v>
+        <v>13.636363636363</v>
       </c>
       <c r="F21" s="17">
         <v>119</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>21.428571428571</v>
+        <v>33.707865168539</v>
       </c>
       <c r="I21" s="17">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="J21" s="17">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="K21" s="18">
-        <v>5.414012738853</v>
+        <v>6.845238095238</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.498542274052</v>
+        <v>-1.101928374655</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.809264305177</v>
+        <v>-6.994818652849</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.172343670564</v>
+        <v>-82.839388145315</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
+        <v>-27.272727272727</v>
+      </c>
+      <c r="F24" s="14">
+        <v>75</v>
+      </c>
+      <c r="G24" s="14">
+        <v>90</v>
+      </c>
+      <c r="H24" s="15">
         <v>-16.666666666666</v>
       </c>
-      <c r="F24" s="14">
-        <v>78</v>
-      </c>
-      <c r="G24" s="14">
-        <v>104</v>
-      </c>
-      <c r="H24" s="15">
-        <v>-25</v>
-      </c>
       <c r="I24" s="14">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="J24" s="14">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.579545454545</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L24" s="15">
-        <v>-32.581453634085</v>
+        <v>-33.021077283372</v>
       </c>
       <c r="M24" s="15">
-        <v>24.537037037037</v>
+        <v>26.548672566371</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>-80</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H25" s="15">
-        <v>-48.333333333333</v>
+        <v>-48.979591836734</v>
       </c>
       <c r="I25" s="14">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J25" s="14">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.931818181818</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.005181347150</v>
+        <v>-45.049504950495</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>71.428571428571</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F26" s="14">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>34.090909090909</v>
+        <v>10.204081632653</v>
       </c>
       <c r="I26" s="14">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="J26" s="14">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="K26" s="15">
-        <v>11.278195488721</v>
+        <v>10.416666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.904761904761</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.732484076433</v>
+        <v>-7.558139534883</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,22 +1397,22 @@
         <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="L27" s="15">
-        <v>71.428571428571</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-27.272727272727</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>18.181818181818</v>
+        <v>4.347826086956</v>
       </c>
       <c r="L28" s="15">
-        <v>160</v>
+        <v>118.181818181818</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,26 +1551,26 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>233.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="L15" s="15">
-        <v>42.857142857142</v>
+        <v>10</v>
       </c>
       <c r="M15" s="15">
-        <v>900</v>
+        <v>450</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>160</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>5.128205128205</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.846153846153</v>
+        <v>-26.785714285714</v>
       </c>
       <c r="M16" s="15">
-        <v>-50.666666666666</v>
+        <v>-51.190476190476</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.664804469273</v>
+        <v>-89.095744680851</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>8</v>
+      </c>
+      <c r="D17" s="14">
         <v>5</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>66.666666666666</v>
+        <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
         <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I17" s="14">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J17" s="14">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K17" s="15">
-        <v>17.441860465116</v>
+        <v>19.780219780219</v>
       </c>
       <c r="L17" s="15">
-        <v>6.315789473684</v>
+        <v>3.809523809523</v>
       </c>
       <c r="M17" s="15">
-        <v>57.8125</v>
+        <v>55.714285714285</v>
       </c>
       <c r="N17" s="15">
-        <v>9.782608695652</v>
+        <v>14.736842105263</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>4</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>9.090909090909</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-8.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.75</v>
+        <v>-56.790123456790</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.624365482233</v>
+        <v>-91.725768321513</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-30</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>7.407407407407</v>
+        <v>-5</v>
       </c>
       <c r="I19" s="14">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J19" s="14">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.526315789473</v>
+        <v>-9.278350515463</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.047619047619</v>
+        <v>-20.720720720720</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.593406593406</v>
+        <v>-12.871287128712</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.078947368421</v>
+        <v>-45</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F20" s="14">
+        <v>27</v>
+      </c>
+      <c r="G20" s="14">
+        <v>27</v>
+      </c>
+      <c r="H20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="14">
-        <v>30</v>
-      </c>
-      <c r="G20" s="14">
-        <v>26</v>
-      </c>
-      <c r="H20" s="15">
-        <v>15.384615384615</v>
-      </c>
       <c r="I20" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J20" s="14">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K20" s="15">
-        <v>15.384615384615</v>
+        <v>10.588235294117</v>
       </c>
       <c r="L20" s="15">
-        <v>26.760563380281</v>
+        <v>16.049382716049</v>
       </c>
       <c r="M20" s="15">
-        <v>21.621621621621</v>
+        <v>20.512820512820</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.682070240295</v>
+        <v>-91.754385964912</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>13.636363636363</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>33.707865168539</v>
+        <v>27.5</v>
       </c>
       <c r="I21" s="17">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="J21" s="17">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="K21" s="18">
-        <v>6.845238095238</v>
+        <v>7.022471910112</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.101928374655</v>
+        <v>-4.511278195488</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.994818652849</v>
+        <v>-8.633093525179</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.839388145315</v>
+        <v>-82.744565217391</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E24" s="15">
-        <v>-27.272727272727</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.666666666666</v>
+        <v>-30.097087378640</v>
       </c>
       <c r="I24" s="14">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="J24" s="14">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.529411764705</v>
+        <v>-26.650366748166</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.021077283372</v>
+        <v>-34.210526315789</v>
       </c>
       <c r="M24" s="15">
-        <v>26.548672566371</v>
+        <v>23.456790123456</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E25" s="15">
-        <v>-90.909090909090</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H25" s="15">
-        <v>-48.979591836734</v>
+        <v>-62.5</v>
       </c>
       <c r="I25" s="14">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J25" s="14">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="K25" s="15">
-        <v>-36.931818181818</v>
+        <v>-40.816326530612</v>
       </c>
       <c r="L25" s="15">
-        <v>-45.049504950495</v>
+        <v>-45.794392523364</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-9.090909090909</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>10.204081632653</v>
+        <v>32.5</v>
       </c>
       <c r="I26" s="14">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="J26" s="14">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="K26" s="15">
-        <v>10.416666666666</v>
+        <v>7.643312101910</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.169491525423</v>
+        <v>-12.886597938144</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.558139534883</v>
+        <v>-8.152173913043</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="L27" s="15">
-        <v>44.444444444444</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K28" s="15">
-        <v>4.347826086956</v>
+        <v>-4</v>
       </c>
       <c r="L28" s="15">
         <v>118.181818181818</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
         <v>-90.909090909090</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
         <v>-88.888888888888</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1610,17 +1610,17 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="J33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L33" s="15">
         <v>-66.666666666666</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>266.666666666667</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M15" s="15">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="N15" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>133.333333333333</v>
+        <v>88.888888888888</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J16" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K16" s="15">
-        <v>5.128205128205</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.785714285714</v>
+        <v>-29.6875</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.190476190476</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.095744680851</v>
+        <v>-88.607594936708</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>60</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>40</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I17" s="14">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J17" s="14">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K17" s="15">
-        <v>19.780219780219</v>
+        <v>15.306122448979</v>
       </c>
       <c r="L17" s="15">
-        <v>3.809523809523</v>
+        <v>0.892857142857</v>
       </c>
       <c r="M17" s="15">
-        <v>55.714285714285</v>
+        <v>59.154929577464</v>
       </c>
       <c r="N17" s="15">
-        <v>14.736842105263</v>
+        <v>6.603773584905</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,10 +1019,10 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>10</v>
@@ -1034,22 +1034,22 @@
         <v>42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>-12.5</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="L18" s="15">
-        <v>-2.777777777777</v>
+        <v>2.777777777777</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.790123456790</v>
+        <v>-55.952380952380</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.725768321513</v>
+        <v>-91.685393258427</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>4</v>
+      </c>
+      <c r="D19" s="14">
         <v>3</v>
       </c>
-      <c r="D19" s="14">
-        <v>2</v>
-      </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H19" s="15">
-        <v>-5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.278350515463</v>
+        <v>-7</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.720720720720</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="M19" s="15">
-        <v>-12.871287128712</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="N19" s="15">
-        <v>-45</v>
+        <v>-46.857142857142</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F20" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
         <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I20" s="14">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J20" s="14">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K20" s="15">
-        <v>10.588235294117</v>
+        <v>6.521739130434</v>
       </c>
       <c r="L20" s="15">
-        <v>16.049382716049</v>
+        <v>13.953488372093</v>
       </c>
       <c r="M20" s="15">
-        <v>20.512820512820</v>
+        <v>20.987654320987</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.754385964912</v>
+        <v>-91.880695940348</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F21" s="17">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H21" s="18">
-        <v>27.5</v>
+        <v>11.904761904761</v>
       </c>
       <c r="I21" s="17">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="J21" s="17">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="K21" s="18">
-        <v>7.022471910112</v>
+        <v>5.804749340369</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.511278195488</v>
+        <v>-6.960556844547</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.633093525179</v>
+        <v>-7.603686635944</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.744565217391</v>
+        <v>-82.877882152006</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-57.142857142857</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G24" s="14">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>-30.097087378640</v>
+        <v>-36.633663366336</v>
       </c>
       <c r="I24" s="14">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="J24" s="14">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="K24" s="15">
-        <v>-26.650366748166</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="L24" s="15">
-        <v>-34.210526315789</v>
+        <v>-34.917355371900</v>
       </c>
       <c r="M24" s="15">
-        <v>23.456790123456</v>
+        <v>23.529411764705</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-75</v>
+        <v>-78.947368421052</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>-62.5</v>
+        <v>-80</v>
       </c>
       <c r="I25" s="14">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J25" s="14">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="K25" s="15">
-        <v>-40.816326530612</v>
+        <v>-44.651162790697</v>
       </c>
       <c r="L25" s="15">
-        <v>-45.794392523364</v>
+        <v>-48.260869565217</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.384615384615</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="F26" s="14">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H26" s="15">
-        <v>32.5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J26" s="14">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="K26" s="15">
-        <v>7.643312101910</v>
+        <v>1.149425287356</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.886597938144</v>
+        <v>-18.894009216589</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.152173913043</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1444,16 +1444,16 @@
         <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J28" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K28" s="15">
-        <v>-4</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="L28" s="15">
-        <v>118.181818181818</v>
+        <v>92.307692307692</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-102pct.xlsx
+++ b/data/source/weekly/cs-en-us-102pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -878,11 +878,11 @@
       <c r="K14" s="15">
         <v>200</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>200</v>
       </c>
       <c r="M14" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N14" s="15">
         <v>-25</v>
@@ -896,37 +896,37 @@
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>116.666666666667</v>
       </c>
       <c r="L15" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M15" s="15">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="N15" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>88.888888888888</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I16" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K16" s="15">
-        <v>7.142857142857</v>
+        <v>6.521739130434</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.6875</v>
+        <v>-24.615384615384</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.275862068965</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.607594936708</v>
+        <v>-88.077858880778</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-42.857142857142</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.090909090909</v>
+        <v>23.809523809523</v>
       </c>
       <c r="I17" s="14">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="J17" s="14">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K17" s="15">
-        <v>15.306122448979</v>
+        <v>18.269230769230</v>
       </c>
       <c r="L17" s="15">
-        <v>0.892857142857</v>
+        <v>0.819672131147</v>
       </c>
       <c r="M17" s="15">
-        <v>59.154929577464</v>
+        <v>68.493150684931</v>
       </c>
       <c r="N17" s="15">
-        <v>6.603773584905</v>
+        <v>6.956521739130</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="E18" s="15">
-        <v>-50</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J18" s="14">
         <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.904761904761</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L18" s="15">
-        <v>2.777777777777</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.952380952380</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.685393258427</v>
+        <v>-91.684434968017</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
         <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J19" s="14">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K19" s="15">
-        <v>-7</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.390243902439</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.888888888888</v>
+        <v>-12.068965517241</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.857142857142</v>
+        <v>-44.864864864864</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>-57.142857142857</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>-11.111111111111</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="I20" s="14">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J20" s="14">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="K20" s="15">
-        <v>6.521739130434</v>
+        <v>2.912621359223</v>
       </c>
       <c r="L20" s="15">
-        <v>13.953488372093</v>
+        <v>15.217391304347</v>
       </c>
       <c r="M20" s="15">
-        <v>20.987654320987</v>
+        <v>27.710843373494</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.880695940348</v>
+        <v>-91.646966115051</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.739130434782</v>
+        <v>10.344827586206</v>
       </c>
       <c r="F21" s="17">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G21" s="17">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>11.904761904761</v>
+        <v>-1.075268817204</v>
       </c>
       <c r="I21" s="17">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="J21" s="17">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="K21" s="18">
-        <v>5.804749340369</v>
+        <v>6.617647058823</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.960556844547</v>
+        <v>-3.761061946902</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.603686635944</v>
+        <v>-5.434782608695</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.877882152006</v>
+        <v>-82.338611449451</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.461538461538</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="F24" s="14">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H24" s="15">
-        <v>-36.633663366336</v>
+        <v>-44.339622641509</v>
       </c>
       <c r="I24" s="14">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="J24" s="14">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="K24" s="15">
-        <v>-27.586206896551</v>
+        <v>-28.82096069869</v>
       </c>
       <c r="L24" s="15">
-        <v>-34.917355371900</v>
+        <v>-37.186897880539</v>
       </c>
       <c r="M24" s="15">
-        <v>23.529411764705</v>
+        <v>18.545454545454</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-78.947368421052</v>
+        <v>-87.5</v>
       </c>
       <c r="F25" s="14">
         <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H25" s="15">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="I25" s="14">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J25" s="14">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="K25" s="15">
-        <v>-44.651162790697</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="L25" s="15">
-        <v>-48.260869565217</v>
+        <v>-50.205761316872</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>11</v>
+      </c>
+      <c r="D26" s="14">
         <v>6</v>
       </c>
-      <c r="D26" s="14">
-        <v>17</v>
-      </c>
       <c r="E26" s="15">
-        <v>-64.705882352941</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G26" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>-16.666666666666</v>
+        <v>-17.021276595744</v>
       </c>
       <c r="I26" s="14">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="J26" s="14">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="K26" s="15">
-        <v>1.149425287356</v>
+        <v>5</v>
       </c>
       <c r="L26" s="15">
-        <v>-18.894009216589</v>
+        <v>-15.625</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.204081632653</v>
+        <v>-7.804878048780</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I28" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J28" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K28" s="15">
-        <v>-7.407407407407</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="L28" s="15">
-        <v>92.307692307692</v>
+        <v>107.692307692308</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
         <v>-92.857142857142</v>
@@ -1535,10 +1535,10 @@
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
         <v>-90</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1570,7 +1570,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
         <v>-100</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,26 +1616,26 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
